--- a/data/trans_orig/IP25-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP25-Provincia-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40252</t>
+          <t>40524</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48404</t>
+          <t>48474</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>47681</t>
+          <t>48629</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56750</t>
+          <t>56732</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>92029</t>
+          <t>92080</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>103539</t>
+          <t>103602</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,86%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4164</t>
+          <t>4094</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12316</t>
+          <t>12044</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3467</t>
+          <t>3485</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12536</t>
+          <t>11588</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9246</t>
+          <t>9183</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20756</t>
+          <t>20705</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,36%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82760</t>
+          <t>83066</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>93690</t>
+          <t>93549</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>88988</t>
+          <t>89675</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>100281</t>
+          <t>100250</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>176346</t>
+          <t>176115</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>191705</t>
+          <t>191152</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>90,89%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7872</t>
+          <t>8013</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18802</t>
+          <t>18496</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8476</t>
+          <t>8507</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19769</t>
+          <t>19082</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>18614</t>
+          <t>19167</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>33973</t>
+          <t>34204</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,26%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56949</t>
+          <t>57166</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64844</t>
+          <t>64831</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>61545</t>
+          <t>62115</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68450</t>
+          <t>68456</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>122675</t>
+          <t>122001</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>132232</t>
+          <t>132008</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,71%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>2766</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10648</t>
+          <t>10431</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1877</t>
+          <t>1871</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8782</t>
+          <t>8212</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5692</t>
+          <t>5916</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>15249</t>
+          <t>15923</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>65541</t>
+          <t>65439</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>72941</t>
+          <t>72958</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67197</t>
+          <t>67426</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76160</t>
+          <t>76164</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>136664</t>
+          <t>136315</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>147265</t>
+          <t>147587</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,85%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>1903</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9320</t>
+          <t>9422</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>2947</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11914</t>
+          <t>11685</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6707</t>
+          <t>6385</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17308</t>
+          <t>17657</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,47%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29319</t>
+          <t>29739</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37334</t>
+          <t>37406</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29681</t>
+          <t>30053</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>38692</t>
+          <t>38684</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>62606</t>
+          <t>62090</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>74618</t>
+          <t>75076</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>86,6%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4518</t>
+          <t>4446</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12533</t>
+          <t>12113</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6151</t>
+          <t>6159</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15162</t>
+          <t>14790</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12077</t>
+          <t>11619</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>24089</t>
+          <t>24605</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>28,38%</t>
         </is>
       </c>
     </row>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>47419</t>
+          <t>47918</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>49363</t>
+          <t>49570</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>56731</t>
+          <t>56893</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>100804</t>
+          <t>100074</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>110357</t>
+          <t>110197</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,17%</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8636</t>
+          <t>8137</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>2839</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>10162</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5430</t>
+          <t>5590</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14983</t>
+          <t>15713</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,57%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>114053</t>
+          <t>113724</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>123132</t>
+          <t>122920</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>112082</t>
+          <t>111861</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>124682</t>
+          <t>124599</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>229418</t>
+          <t>229957</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>244771</t>
+          <t>245329</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,34%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4046</t>
+          <t>4258</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13125</t>
+          <t>13454</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>10973</t>
+          <t>11056</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>23573</t>
+          <t>23794</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>18062</t>
+          <t>17504</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>33415</t>
+          <t>32876</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,51%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>135606</t>
+          <t>135781</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>147954</t>
+          <t>147674</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>128671</t>
+          <t>128022</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>144054</t>
+          <t>143197</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>268813</t>
+          <t>268259</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>288109</t>
+          <t>288560</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,63%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9950</t>
+          <t>10230</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>22298</t>
+          <t>22123</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>20004</t>
+          <t>20861</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>35387</t>
+          <t>36036</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>33853</t>
+          <t>33402</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>53149</t>
+          <t>53703</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,68%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>601092</t>
+          <t>600298</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>625225</t>
+          <t>625132</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>616993</t>
+          <t>616543</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>645702</t>
+          <t>645662</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1227233</t>
+          <t>1227346</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1264402</t>
+          <t>1263383</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,1%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>54352</t>
+          <t>54445</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>78485</t>
+          <t>79279</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>76998</t>
+          <t>77038</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>105707</t>
+          <t>106157</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>137875</t>
+          <t>138894</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>175044</t>
+          <t>174931</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,47%</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>49668</t>
+          <t>49243</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>55478</t>
+          <t>55145</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>63013</t>
+          <t>63017</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>107849</t>
+          <t>107642</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>117733</t>
+          <t>117760</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,34%</t>
         </is>
       </c>
     </row>
@@ -4173,7 +4173,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7759</t>
+          <t>8184</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>1792</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9331</t>
+          <t>9664</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4503</t>
+          <t>4476</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14387</t>
+          <t>14594</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82198</t>
+          <t>82329</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>94123</t>
+          <t>94086</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>93463</t>
+          <t>91983</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>104021</t>
+          <t>103702</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>180344</t>
+          <t>179387</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>195711</t>
+          <t>195553</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,59%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10590</t>
+          <t>10627</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22515</t>
+          <t>22384</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7138</t>
+          <t>7457</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17696</t>
+          <t>19176</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>20161</t>
+          <t>20319</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>35528</t>
+          <t>36485</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,9%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>58369</t>
+          <t>58113</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65459</t>
+          <t>65501</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63093</t>
+          <t>63019</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>69860</t>
+          <t>69857</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>124111</t>
+          <t>124211</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>133797</t>
+          <t>133944</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,06%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2719</t>
+          <t>2677</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9809</t>
+          <t>10065</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t>8235</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5635</t>
+          <t>5488</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>15321</t>
+          <t>15221</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,92%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>65440</t>
+          <t>65584</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>73970</t>
+          <t>74487</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68574</t>
+          <t>68519</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77962</t>
+          <t>78108</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>137879</t>
+          <t>137967</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>150218</t>
+          <t>150516</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>94,08%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3791</t>
+          <t>3274</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12321</t>
+          <t>12177</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4272</t>
+          <t>4126</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13660</t>
+          <t>13715</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9777</t>
+          <t>9479</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22116</t>
+          <t>22028</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,77%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>38449</t>
+          <t>38253</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43256</t>
+          <t>43250</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>41106</t>
+          <t>40755</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>46084</t>
+          <t>46085</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>82141</t>
+          <t>82088</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>89150</t>
+          <t>89142</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,33%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>651</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5452</t>
+          <t>5648</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>667</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5646</t>
+          <t>5997</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8512</t>
+          <t>8565</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45921</t>
+          <t>46482</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>53694</t>
+          <t>53833</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50577</t>
+          <t>50001</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>58317</t>
+          <t>58145</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>99898</t>
+          <t>99977</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>110874</t>
+          <t>110541</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,11%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2291</t>
+          <t>2152</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10064</t>
+          <t>9503</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1928</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9668</t>
+          <t>10244</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>5689</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>16332</t>
+          <t>16253</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,98%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>110084</t>
+          <t>109875</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>124430</t>
+          <t>123738</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>122716</t>
+          <t>121892</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>134619</t>
+          <t>135234</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>235932</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>254573</t>
+          <t>256017</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,62%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13347</t>
+          <t>14039</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>27693</t>
+          <t>27902</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>10135</t>
+          <t>9520</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>22038</t>
+          <t>22862</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>27958</t>
+          <t>26514</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>46599</t>
+          <t>45401</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,07%</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>140528</t>
+          <t>139512</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>152832</t>
+          <t>152429</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>146954</t>
+          <t>148620</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>159438</t>
+          <t>160248</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>291047</t>
+          <t>291940</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>309594</t>
+          <t>309513</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,67%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11876</t>
+          <t>12279</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>24180</t>
+          <t>25196</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>9836</t>
+          <t>9026</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>22320</t>
+          <t>20654</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>24388</t>
+          <t>24469</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>42935</t>
+          <t>42042</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,59%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>617612</t>
+          <t>618615</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>645912</t>
+          <t>646696</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>672442</t>
+          <t>670650</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>697686</t>
+          <t>697623</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1299481</t>
+          <t>1298862</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1335811</t>
+          <t>1337184</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,53%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>64538</t>
+          <t>63754</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>92838</t>
+          <t>91835</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>52796</t>
+          <t>52859</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>78040</t>
+          <t>79832</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>125120</t>
+          <t>123747</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>161450</t>
+          <t>162069</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -7378,12 +7378,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43036</t>
+          <t>43385</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52121</t>
+          <t>52313</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7393,12 +7393,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>52152</t>
+          <t>51570</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>60417</t>
+          <t>60488</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>98809</t>
+          <t>98962</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>111066</t>
+          <t>111830</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7463,12 +7463,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,79%</t>
         </is>
       </c>
     </row>
@@ -7491,12 +7491,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5058</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14335</t>
+          <t>13986</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4045</t>
+          <t>3974</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12310</t>
+          <t>12892</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10767</t>
+          <t>10003</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23024</t>
+          <t>22871</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,77%</t>
         </is>
       </c>
     </row>
@@ -7721,12 +7721,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>91618</t>
+          <t>90897</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>99836</t>
+          <t>99241</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7736,12 +7736,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>101590</t>
+          <t>101283</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>108332</t>
+          <t>108316</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7771,12 +7771,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>194974</t>
+          <t>195730</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>206134</t>
+          <t>206420</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7806,12 +7806,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,35%</t>
         </is>
       </c>
     </row>
@@ -7834,12 +7834,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>4706</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12329</t>
+          <t>13050</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8693</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>7810</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>19256</t>
+          <t>18500</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7919,12 +7919,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -8064,12 +8064,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50644</t>
+          <t>51122</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60953</t>
+          <t>61154</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8079,12 +8079,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>53369</t>
+          <t>53255</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63152</t>
+          <t>63259</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8114,12 +8114,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>108090</t>
+          <t>108199</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>121766</t>
+          <t>122213</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,38%</t>
         </is>
       </c>
     </row>
@@ -8177,12 +8177,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>5677</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16187</t>
+          <t>15709</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8192,12 +8192,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6753</t>
+          <t>6646</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16536</t>
+          <t>16650</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8227,12 +8227,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14970</t>
+          <t>14523</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>28646</t>
+          <t>28537</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8262,12 +8262,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,87%</t>
         </is>
       </c>
     </row>
@@ -8407,12 +8407,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62427</t>
+          <t>62803</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71737</t>
+          <t>71775</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8422,12 +8422,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8442,12 +8442,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71339</t>
+          <t>71267</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>79178</t>
+          <t>79469</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8457,12 +8457,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>137326</t>
+          <t>136690</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>149244</t>
+          <t>149361</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,45%</t>
         </is>
       </c>
     </row>
@@ -8520,12 +8520,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>5186</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14534</t>
+          <t>14158</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8535,12 +8535,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>1715</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9845</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8570,12 +8570,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8901</t>
+          <t>8784</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>20819</t>
+          <t>21455</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,57%</t>
         </is>
       </c>
     </row>
@@ -8750,12 +8750,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35912</t>
+          <t>35528</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41747</t>
+          <t>42111</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8785,12 +8785,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34364</t>
+          <t>34715</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43144</t>
+          <t>43047</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8800,12 +8800,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8820,12 +8820,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>73570</t>
+          <t>74322</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>83905</t>
+          <t>84065</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,63%</t>
         </is>
       </c>
     </row>
@@ -8863,12 +8863,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1691</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7526</t>
+          <t>7910</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8898,12 +8898,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>3303</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11986</t>
+          <t>11635</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8913,12 +8913,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8933,12 +8933,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5883</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16218</t>
+          <t>15466</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,23%</t>
         </is>
       </c>
     </row>
@@ -9093,12 +9093,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45390</t>
+          <t>44524</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>52352</t>
+          <t>52308</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9128,12 +9128,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50091</t>
+          <t>49921</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>56382</t>
+          <t>56389</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9143,12 +9143,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>98010</t>
+          <t>98042</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>107349</t>
+          <t>107414</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,9%</t>
         </is>
       </c>
     </row>
@@ -9206,12 +9206,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8883</t>
+          <t>9749</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9241,12 +9241,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1357</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7648</t>
+          <t>7818</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9256,12 +9256,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4663</t>
+          <t>4598</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14002</t>
+          <t>13970</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,47%</t>
         </is>
       </c>
     </row>
@@ -9436,12 +9436,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>120757</t>
+          <t>120237</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>130644</t>
+          <t>130778</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9471,12 +9471,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>121864</t>
+          <t>121507</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>133794</t>
+          <t>133808</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>246274</t>
+          <t>247075</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>261642</t>
+          <t>262431</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,24%</t>
         </is>
       </c>
     </row>
@@ -9549,12 +9549,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6730</t>
+          <t>6596</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>16617</t>
+          <t>17137</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9584,12 +9584,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>10278</t>
+          <t>10264</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>22208</t>
+          <t>22565</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9599,12 +9599,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>19804</t>
+          <t>19015</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>35172</t>
+          <t>34371</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,21%</t>
         </is>
       </c>
     </row>
@@ -9779,12 +9779,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>140527</t>
+          <t>140315</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>152692</t>
+          <t>152492</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9794,12 +9794,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>152030</t>
+          <t>153570</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>163655</t>
+          <t>163917</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>299079</t>
+          <t>297409</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>314143</t>
+          <t>313714</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,64%</t>
         </is>
       </c>
     </row>
@@ -9892,12 +9892,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11484</t>
+          <t>11684</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>23649</t>
+          <t>23861</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9907,12 +9907,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7194</t>
+          <t>6932</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>18819</t>
+          <t>17279</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9942,12 +9942,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>20882</t>
+          <t>21311</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>35946</t>
+          <t>37616</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>11,23%</t>
         </is>
       </c>
     </row>
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>618103</t>
+          <t>618652</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>644853</t>
+          <t>644628</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>666379</t>
+          <t>666188</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>691435</t>
+          <t>691607</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10172,12 +10172,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1292026</t>
+          <t>1294340</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1329840</t>
+          <t>1330065</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,78%</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>59518</t>
+          <t>59743</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>86268</t>
+          <t>85719</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>53409</t>
+          <t>53237</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>78465</t>
+          <t>78656</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>119375</t>
+          <t>119150</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>157189</t>
+          <t>154875</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
